--- a/run/nhanes_pullrequest_IndVsArea_09012026.xlsx
+++ b/run/nhanes_pullrequest_IndVsArea_09012026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jg1671/Documents/GitHub/nhanes_area_ses/run/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22639D1A-F44F-F147-9872-55B29A728CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB99C84-161B-4346-B851-C4C50B769834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67860" yWindow="960" windowWidth="31460" windowHeight="17840" xr2:uid="{BFFDAA01-B797-C24A-A87F-A362CCE94DEB}"/>
+    <workbookView xWindow="35440" yWindow="5240" windowWidth="28800" windowHeight="16240" xr2:uid="{BFFDAA01-B797-C24A-A87F-A362CCE94DEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable_List" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="788">
   <si>
     <t>Respondent sequence number</t>
   </si>
@@ -2379,6 +2379,27 @@
   </si>
   <si>
     <t>u_bpa</t>
+  </si>
+  <si>
+    <t>qUESTIONNAIRE</t>
+  </si>
+  <si>
+    <t>PHAFSTHR</t>
+  </si>
+  <si>
+    <t>Total length of 'food fast', hours</t>
+  </si>
+  <si>
+    <t>fasting_hr</t>
+  </si>
+  <si>
+    <t>PHAFSTMN</t>
+  </si>
+  <si>
+    <t>Total length of 'food fast', minutes</t>
+  </si>
+  <si>
+    <t>fasting_min</t>
   </si>
 </sst>
 </file>
@@ -2832,7 +2853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3D6F9ED-9DEC-0147-B030-50BD2869D005}">
-  <dimension ref="A1:G292"/>
+  <dimension ref="A1:G294"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="19.5" style="1" customWidth="1"/>
@@ -3104,7 +3125,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
         <v>83</v>
       </c>
@@ -3121,7 +3142,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
         <v>83</v>
       </c>
@@ -3138,322 +3159,322 @@
         <v>576</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>157</v>
+        <v>782</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>156</v>
+        <v>783</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>346</v>
+        <v>784</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>198</v>
+        <v>785</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>652</v>
+        <v>786</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>653</v>
+        <v>787</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>173</v>
+      <c r="B21" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>296</v>
+        <v>156</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="E21" t="s">
+        <v>346</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>160</v>
+        <v>652</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E22" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>653</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>293</v>
+      <c r="B23" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="E23" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>291</v>
+        <v>159</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>292</v>
+        <v>160</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>347</v>
+      </c>
+      <c r="E24" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>166</v>
+      <c r="B25" s="5" t="s">
+        <v>293</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>161</v>
+        <v>294</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E25" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>167</v>
+      <c r="B26" s="5" t="s">
+        <v>291</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E26" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>349</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E27" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>504</v>
+        <v>161</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>505</v>
+        <v>350</v>
       </c>
       <c r="E28" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>331</v>
+        <v>175</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>330</v>
+        <v>200</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E29" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>184</v>
+        <v>504</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>353</v>
+        <v>505</v>
       </c>
       <c r="E30" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:5">
       <c r="A31" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>170</v>
+        <v>331</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>185</v>
+        <v>330</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E31" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>768</v>
+      <c r="B32" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>769</v>
+        <v>184</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>770</v>
+        <v>353</v>
       </c>
       <c r="E32" t="s">
         <v>577</v>
       </c>
-      <c r="G32" s="4"/>
-    </row>
-    <row r="33" spans="1:5">
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E33" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:7">
       <c r="A34" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>332</v>
+      <c r="B34" s="5" t="s">
+        <v>768</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>333</v>
+        <v>769</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>360</v>
+        <v>770</v>
       </c>
       <c r="E34" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E35" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:7">
       <c r="A36" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E36" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:7">
       <c r="A37" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>355</v>
@@ -3462,188 +3483,188 @@
         <v>577</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:7">
       <c r="A38" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>188</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>192</v>
+        <v>335</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="E38" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:7">
       <c r="A39" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E39" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>295</v>
+        <v>192</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E40" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:7">
       <c r="A41" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>654</v>
+        <v>172</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>655</v>
+        <v>187</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>658</v>
+        <v>356</v>
       </c>
       <c r="E41" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>656</v>
+        <v>174</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>657</v>
+        <v>295</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>658</v>
+        <v>357</v>
       </c>
       <c r="E42" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:7">
       <c r="A43" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="E43" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:7">
       <c r="A44" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="E44" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:7">
       <c r="A45" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="E45" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:7">
       <c r="A46" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="E46" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>197</v>
+        <v>665</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>196</v>
+        <v>666</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E47" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:7">
       <c r="A48" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>181</v>
+        <v>667</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E48" t="s">
         <v>577</v>
@@ -3654,13 +3675,13 @@
         <v>155</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>672</v>
+        <v>197</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>675</v>
+        <v>196</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="E49" t="s">
         <v>577</v>
@@ -3671,13 +3692,13 @@
         <v>155</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>673</v>
+        <v>181</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="E50" t="s">
         <v>577</v>
@@ -3688,13 +3709,13 @@
         <v>155</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E51" t="s">
         <v>577</v>
@@ -3705,13 +3726,13 @@
         <v>155</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E52" t="s">
         <v>577</v>
@@ -3722,13 +3743,13 @@
         <v>155</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="E53" t="s">
         <v>577</v>
@@ -3739,13 +3760,13 @@
         <v>155</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="E54" t="s">
         <v>577</v>
@@ -3756,13 +3777,13 @@
         <v>155</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>183</v>
+        <v>682</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>199</v>
+        <v>683</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E55" t="s">
         <v>577</v>
@@ -3773,13 +3794,13 @@
         <v>155</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>182</v>
+        <v>685</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>199</v>
+        <v>686</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E56" t="s">
         <v>577</v>
@@ -3790,10 +3811,10 @@
         <v>155</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>688</v>
+        <v>183</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>689</v>
+        <v>199</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>687</v>
@@ -3807,13 +3828,13 @@
         <v>155</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>690</v>
+        <v>199</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="E58" t="s">
         <v>577</v>
@@ -3824,13 +3845,13 @@
         <v>155</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>177</v>
+        <v>688</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>193</v>
+        <v>689</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="E59" t="s">
         <v>577</v>
@@ -3841,13 +3862,13 @@
         <v>155</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>691</v>
+        <v>176</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E60" t="s">
         <v>577</v>
@@ -3858,13 +3879,13 @@
         <v>155</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>693</v>
+        <v>193</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E61" t="s">
         <v>577</v>
@@ -3875,13 +3896,13 @@
         <v>155</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>179</v>
+        <v>691</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>194</v>
+        <v>692</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E62" t="s">
         <v>577</v>
@@ -3892,13 +3913,13 @@
         <v>155</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>195</v>
+        <v>693</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E63" t="s">
         <v>577</v>
@@ -3909,16 +3930,16 @@
         <v>155</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>694</v>
+        <v>179</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>695</v>
+        <v>194</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>731</v>
+        <v>700</v>
+      </c>
+      <c r="E64" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3926,16 +3947,16 @@
         <v>155</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>703</v>
+        <v>180</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>704</v>
+        <v>195</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>732</v>
+        <v>701</v>
+      </c>
+      <c r="E65" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3943,16 +3964,16 @@
         <v>155</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>772</v>
+        <v>694</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>773</v>
+        <v>695</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>778</v>
+        <v>702</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>774</v>
+        <v>731</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3960,16 +3981,16 @@
         <v>155</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>775</v>
+        <v>703</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>773</v>
+        <v>704</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>774</v>
+        <v>732</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3977,13 +3998,13 @@
         <v>155</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>706</v>
+        <v>772</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>705</v>
+        <v>773</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>774</v>
@@ -3994,13 +4015,13 @@
         <v>155</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>707</v>
+        <v>775</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>705</v>
+        <v>773</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>774</v>
@@ -4011,16 +4032,16 @@
         <v>155</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>733</v>
+        <v>774</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4028,16 +4049,16 @@
         <v>155</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>713</v>
+        <v>776</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>734</v>
+        <v>774</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4045,16 +4066,16 @@
         <v>155</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>713</v>
+        <v>777</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4062,50 +4083,50 @@
         <v>155</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>779</v>
+        <v>713</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="E74" t="s">
-        <v>577</v>
+        <v>713</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="E75" t="s">
-        <v>577</v>
+        <v>779</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4113,13 +4134,13 @@
         <v>162</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E76" t="s">
         <v>577</v>
@@ -4130,13 +4151,13 @@
         <v>162</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E77" t="s">
         <v>577</v>
@@ -4147,13 +4168,13 @@
         <v>162</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E78" t="s">
         <v>577</v>
@@ -4161,16 +4182,16 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>754</v>
+        <v>722</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>755</v>
+        <v>723</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>756</v>
+        <v>729</v>
       </c>
       <c r="E79" t="s">
         <v>577</v>
@@ -4178,36 +4199,36 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>205</v>
+        <v>724</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>524</v>
+        <v>725</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>523</v>
+        <v>730</v>
       </c>
       <c r="E80" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>225</v>
+        <v>754</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>229</v>
+        <v>755</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>365</v>
+        <v>756</v>
       </c>
       <c r="E81" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4215,13 +4236,13 @@
         <v>149</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>228</v>
+        <v>524</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>345</v>
+        <v>523</v>
       </c>
       <c r="E82" t="s">
         <v>576</v>
@@ -4232,13 +4253,13 @@
         <v>149</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>344</v>
+        <v>229</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="E83" t="s">
         <v>576</v>
@@ -4249,13 +4270,13 @@
         <v>149</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E84" t="s">
         <v>576</v>
@@ -4266,13 +4287,13 @@
         <v>149</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>206</v>
+        <v>344</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E85" t="s">
         <v>576</v>
@@ -4283,13 +4304,13 @@
         <v>149</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>342</v>
+        <v>203</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E86" t="s">
         <v>576</v>
@@ -4300,13 +4321,13 @@
         <v>149</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>366</v>
+        <v>206</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>385</v>
+        <v>341</v>
       </c>
       <c r="E87" t="s">
         <v>576</v>
@@ -4317,13 +4338,13 @@
         <v>149</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>381</v>
+        <v>342</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>382</v>
+        <v>343</v>
       </c>
       <c r="E88" t="s">
         <v>576</v>
@@ -4334,13 +4355,13 @@
         <v>149</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="E89" t="s">
         <v>576</v>
@@ -4351,13 +4372,13 @@
         <v>149</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>496</v>
+        <v>382</v>
       </c>
       <c r="E90" t="s">
         <v>576</v>
@@ -4368,13 +4389,13 @@
         <v>149</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E91" t="s">
         <v>576</v>
@@ -4385,13 +4406,13 @@
         <v>149</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>220</v>
+        <v>326</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="E92" t="s">
         <v>576</v>
@@ -4402,13 +4423,13 @@
         <v>149</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>497</v>
+        <v>224</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>498</v>
+        <v>364</v>
       </c>
       <c r="E93" t="s">
         <v>576</v>
@@ -4419,13 +4440,13 @@
         <v>149</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>497</v>
+        <v>220</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>498</v>
+        <v>362</v>
       </c>
       <c r="E94" t="s">
         <v>576</v>
@@ -4436,13 +4457,13 @@
         <v>149</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>321</v>
+        <v>497</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>336</v>
+        <v>498</v>
       </c>
       <c r="E95" t="s">
         <v>576</v>
@@ -4453,13 +4474,13 @@
         <v>149</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>321</v>
+        <v>497</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>336</v>
+        <v>498</v>
       </c>
       <c r="E96" t="s">
         <v>576</v>
@@ -4470,13 +4491,13 @@
         <v>149</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>367</v>
+        <v>211</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>369</v>
+        <v>321</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="E97" t="s">
         <v>576</v>
@@ -4487,13 +4508,13 @@
         <v>149</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>368</v>
+        <v>213</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>369</v>
+        <v>321</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="E98" t="s">
         <v>576</v>
@@ -4504,13 +4525,13 @@
         <v>149</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>520</v>
+        <v>367</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E99" t="s">
         <v>576</v>
@@ -4521,13 +4542,13 @@
         <v>149</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>521</v>
+        <v>368</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E100" t="s">
         <v>576</v>
@@ -4538,13 +4559,13 @@
         <v>149</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>371</v>
+        <v>520</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>522</v>
+        <v>373</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>519</v>
+        <v>374</v>
       </c>
       <c r="E101" t="s">
         <v>576</v>
@@ -4555,13 +4576,13 @@
         <v>149</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>372</v>
+        <v>521</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>522</v>
+        <v>373</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>519</v>
+        <v>374</v>
       </c>
       <c r="E102" t="s">
         <v>576</v>
@@ -4572,13 +4593,13 @@
         <v>149</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>217</v>
+        <v>371</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>324</v>
+        <v>522</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>338</v>
+        <v>519</v>
       </c>
       <c r="E103" t="s">
         <v>576</v>
@@ -4589,13 +4610,13 @@
         <v>149</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>216</v>
+        <v>372</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>324</v>
+        <v>522</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>338</v>
+        <v>519</v>
       </c>
       <c r="E104" t="s">
         <v>576</v>
@@ -4606,13 +4627,13 @@
         <v>149</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>495</v>
+        <v>338</v>
       </c>
       <c r="E105" t="s">
         <v>576</v>
@@ -4623,13 +4644,13 @@
         <v>149</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E106" t="s">
         <v>576</v>
@@ -4640,13 +4661,13 @@
         <v>149</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>339</v>
+        <v>495</v>
       </c>
       <c r="E107" t="s">
         <v>576</v>
@@ -4657,13 +4678,13 @@
         <v>149</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>517</v>
+        <v>219</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E108" t="s">
         <v>576</v>
@@ -4674,13 +4695,13 @@
         <v>149</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E109" t="s">
         <v>576</v>
@@ -4691,13 +4712,13 @@
         <v>149</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>503</v>
+        <v>337</v>
       </c>
       <c r="E110" t="s">
         <v>576</v>
@@ -4708,13 +4729,13 @@
         <v>149</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>503</v>
+        <v>337</v>
       </c>
       <c r="E111" t="s">
         <v>576</v>
@@ -4725,13 +4746,13 @@
         <v>149</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>574</v>
+        <v>518</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>573</v>
+        <v>322</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>575</v>
+        <v>503</v>
       </c>
       <c r="E112" t="s">
         <v>576</v>
@@ -4742,13 +4763,13 @@
         <v>149</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>572</v>
+        <v>214</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>573</v>
+        <v>322</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>575</v>
+        <v>503</v>
       </c>
       <c r="E113" t="s">
         <v>576</v>
@@ -4759,13 +4780,13 @@
         <v>149</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>212</v>
+        <v>574</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>375</v>
+        <v>573</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>377</v>
+        <v>575</v>
       </c>
       <c r="E114" t="s">
         <v>576</v>
@@ -4776,13 +4797,13 @@
         <v>149</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>376</v>
+        <v>572</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>375</v>
+        <v>573</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>377</v>
+        <v>575</v>
       </c>
       <c r="E115" t="s">
         <v>576</v>
@@ -4793,13 +4814,13 @@
         <v>149</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>255</v>
+        <v>212</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>256</v>
+        <v>375</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E116" t="s">
         <v>576</v>
@@ -4810,13 +4831,13 @@
         <v>149</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>230</v>
+        <v>376</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E117" t="s">
         <v>576</v>
@@ -4827,16 +4848,16 @@
         <v>149</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="E118" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -4844,16 +4865,16 @@
         <v>149</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>279</v>
+        <v>230</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>280</v>
+        <v>379</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E119" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -4861,16 +4882,16 @@
         <v>149</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>525</v>
+        <v>233</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>526</v>
+        <v>232</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>577</v>
+        <v>384</v>
+      </c>
+      <c r="E120" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -4878,16 +4899,16 @@
         <v>149</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>528</v>
+        <v>279</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>527</v>
+        <v>280</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>577</v>
+        <v>383</v>
+      </c>
+      <c r="E121" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4895,13 +4916,13 @@
         <v>149</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>577</v>
@@ -4912,13 +4933,13 @@
         <v>149</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>577</v>
@@ -4929,13 +4950,13 @@
         <v>149</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>577</v>
@@ -4946,13 +4967,13 @@
         <v>149</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>577</v>
@@ -4963,13 +4984,13 @@
         <v>149</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>577</v>
@@ -4980,13 +5001,13 @@
         <v>149</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>577</v>
@@ -4997,13 +5018,13 @@
         <v>149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>577</v>
@@ -5014,13 +5035,13 @@
         <v>149</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>577</v>
@@ -5031,13 +5052,13 @@
         <v>149</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>577</v>
@@ -5048,16 +5069,16 @@
         <v>149</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>261</v>
+        <v>544</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>319</v>
+        <v>543</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E131" t="s">
-        <v>576</v>
+        <v>555</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -5065,16 +5086,16 @@
         <v>149</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>609</v>
+        <v>546</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>319</v>
+        <v>545</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E132" t="s">
-        <v>576</v>
+        <v>556</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -5082,13 +5103,13 @@
         <v>149</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>604</v>
+        <v>328</v>
       </c>
       <c r="E133" t="s">
         <v>576</v>
@@ -5099,13 +5120,13 @@
         <v>149</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>604</v>
+        <v>328</v>
       </c>
       <c r="E134" t="s">
         <v>576</v>
@@ -5116,13 +5137,13 @@
         <v>149</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>611</v>
+        <v>262</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>327</v>
+        <v>604</v>
       </c>
       <c r="E135" t="s">
         <v>576</v>
@@ -5133,13 +5154,13 @@
         <v>149</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>260</v>
+        <v>603</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>327</v>
+        <v>604</v>
       </c>
       <c r="E136" t="s">
         <v>576</v>
@@ -5150,13 +5171,13 @@
         <v>149</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>601</v>
+        <v>318</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>608</v>
+        <v>327</v>
       </c>
       <c r="E137" t="s">
         <v>576</v>
@@ -5167,13 +5188,13 @@
         <v>149</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>610</v>
+        <v>260</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>601</v>
+        <v>318</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>608</v>
+        <v>327</v>
       </c>
       <c r="E138" t="s">
         <v>576</v>
@@ -5184,13 +5205,13 @@
         <v>149</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>329</v>
+        <v>608</v>
       </c>
       <c r="E139" t="s">
         <v>576</v>
@@ -5201,13 +5222,13 @@
         <v>149</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>329</v>
+        <v>608</v>
       </c>
       <c r="E140" t="s">
         <v>576</v>
@@ -5218,13 +5239,13 @@
         <v>149</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>590</v>
+        <v>329</v>
       </c>
       <c r="E141" t="s">
         <v>576</v>
@@ -5235,13 +5256,13 @@
         <v>149</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>590</v>
+        <v>329</v>
       </c>
       <c r="E142" t="s">
         <v>576</v>
@@ -5252,7 +5273,7 @@
         <v>149</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>588</v>
@@ -5269,13 +5290,13 @@
         <v>149</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E144" t="s">
         <v>576</v>
@@ -5286,13 +5307,13 @@
         <v>149</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E145" t="s">
         <v>576</v>
@@ -5303,13 +5324,13 @@
         <v>149</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>392</v>
+        <v>591</v>
       </c>
       <c r="E146" t="s">
         <v>576</v>
@@ -5320,13 +5341,13 @@
         <v>149</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>281</v>
+        <v>593</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>282</v>
+        <v>594</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>392</v>
+        <v>591</v>
       </c>
       <c r="E147" t="s">
         <v>576</v>
@@ -5337,13 +5358,13 @@
         <v>149</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>283</v>
+        <v>595</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>391</v>
+        <v>596</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E148" t="s">
         <v>576</v>
@@ -5354,13 +5375,13 @@
         <v>149</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E149" t="s">
         <v>576</v>
@@ -5371,13 +5392,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>311</v>
+        <v>391</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="E150" t="s">
         <v>576</v>
@@ -5388,13 +5409,13 @@
         <v>149</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>312</v>
+        <v>285</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E151" t="s">
         <v>576</v>
@@ -5405,13 +5426,13 @@
         <v>149</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>757</v>
+        <v>286</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>758</v>
+        <v>311</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>759</v>
+        <v>386</v>
       </c>
       <c r="E152" t="s">
         <v>576</v>
@@ -5422,13 +5443,13 @@
         <v>149</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>387</v>
+        <v>312</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="E153" t="s">
         <v>576</v>
@@ -5439,13 +5460,13 @@
         <v>149</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>400</v>
+        <v>757</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>401</v>
+        <v>758</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>404</v>
+        <v>759</v>
       </c>
       <c r="E154" t="s">
         <v>576</v>
@@ -5456,10 +5477,10 @@
         <v>149</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>402</v>
+        <v>288</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>404</v>
@@ -5473,13 +5494,13 @@
         <v>149</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>289</v>
+        <v>400</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="E156" t="s">
         <v>576</v>
@@ -5490,13 +5511,13 @@
         <v>149</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>761</v>
+        <v>402</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>762</v>
+        <v>403</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="E157" t="s">
         <v>576</v>
@@ -5507,7 +5528,7 @@
         <v>149</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>388</v>
+        <v>289</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>389</v>
@@ -5524,13 +5545,13 @@
         <v>149</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>396</v>
+        <v>761</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>397</v>
+        <v>762</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="E159" t="s">
         <v>576</v>
@@ -5541,13 +5562,13 @@
         <v>149</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="E160" t="s">
         <v>576</v>
@@ -5558,13 +5579,13 @@
         <v>149</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>303</v>
+        <v>396</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>306</v>
+        <v>397</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>314</v>
+        <v>399</v>
       </c>
       <c r="E161" t="s">
         <v>576</v>
@@ -5575,13 +5596,13 @@
         <v>149</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>304</v>
+        <v>398</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>307</v>
+        <v>397</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>315</v>
+        <v>399</v>
       </c>
       <c r="E162" t="s">
         <v>576</v>
@@ -5589,16 +5610,16 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2" t="s">
-        <v>149</v>
+        <v>781</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E163" t="s">
         <v>576</v>
@@ -5609,13 +5630,13 @@
         <v>149</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>409</v>
+        <v>315</v>
       </c>
       <c r="E164" t="s">
         <v>576</v>
@@ -5626,13 +5647,13 @@
         <v>149</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>409</v>
+        <v>316</v>
       </c>
       <c r="E165" t="s">
         <v>576</v>
@@ -5643,13 +5664,13 @@
         <v>149</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>405</v>
+        <v>309</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>406</v>
+        <v>310</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E166" t="s">
         <v>576</v>
@@ -5660,13 +5681,13 @@
         <v>149</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>407</v>
+        <v>313</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>406</v>
+        <v>310</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E167" t="s">
         <v>576</v>
@@ -5677,7 +5698,7 @@
         <v>149</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>406</v>
@@ -5694,13 +5715,13 @@
         <v>149</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E169" t="s">
         <v>576</v>
@@ -5711,13 +5732,13 @@
         <v>149</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="E170" t="s">
         <v>576</v>
@@ -5728,13 +5749,13 @@
         <v>149</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E171" t="s">
         <v>576</v>
@@ -5745,13 +5766,13 @@
         <v>149</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E172" t="s">
         <v>576</v>
@@ -5762,13 +5783,13 @@
         <v>149</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E173" t="s">
         <v>576</v>
@@ -5779,10 +5800,10 @@
         <v>149</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>422</v>
@@ -5796,15 +5817,15 @@
         <v>149</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>598</v>
+        <v>423</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>599</v>
+        <v>425</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E175" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E175" t="s">
         <v>576</v>
       </c>
     </row>
@@ -5813,13 +5834,13 @@
         <v>149</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="E176" t="s">
         <v>576</v>
@@ -5830,15 +5851,15 @@
         <v>149</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>432</v>
+        <v>599</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="E177" t="s">
+        <v>429</v>
+      </c>
+      <c r="E177" s="2" t="s">
         <v>576</v>
       </c>
     </row>
@@ -5847,13 +5868,13 @@
         <v>149</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E178" t="s">
         <v>576</v>
@@ -5864,7 +5885,7 @@
         <v>149</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>431</v>
+        <v>600</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>432</v>
@@ -5881,13 +5902,13 @@
         <v>149</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E180" t="s">
         <v>576</v>
@@ -5898,13 +5919,13 @@
         <v>149</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E181" t="s">
         <v>576</v>
@@ -5915,13 +5936,13 @@
         <v>149</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>580</v>
+        <v>435</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>582</v>
+        <v>434</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>585</v>
+        <v>437</v>
       </c>
       <c r="E182" t="s">
         <v>576</v>
@@ -5932,13 +5953,13 @@
         <v>149</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>581</v>
+        <v>436</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>583</v>
+        <v>434</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>584</v>
+        <v>437</v>
       </c>
       <c r="E183" t="s">
         <v>576</v>
@@ -5949,13 +5970,13 @@
         <v>149</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>438</v>
+        <v>580</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>439</v>
+        <v>582</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>452</v>
+        <v>585</v>
       </c>
       <c r="E184" t="s">
         <v>576</v>
@@ -5966,13 +5987,13 @@
         <v>149</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>440</v>
+        <v>581</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>443</v>
+        <v>583</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>453</v>
+        <v>584</v>
       </c>
       <c r="E185" t="s">
         <v>576</v>
@@ -5983,13 +6004,13 @@
         <v>149</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E186" t="s">
         <v>576</v>
@@ -6000,13 +6021,13 @@
         <v>149</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E187" t="s">
         <v>576</v>
@@ -6017,13 +6038,13 @@
         <v>149</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>480</v>
+        <v>454</v>
       </c>
       <c r="E188" t="s">
         <v>576</v>
@@ -6034,13 +6055,13 @@
         <v>149</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E189" t="s">
         <v>576</v>
@@ -6051,13 +6072,13 @@
         <v>149</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="E190" t="s">
         <v>576</v>
@@ -6068,13 +6089,13 @@
         <v>149</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
       <c r="E191" t="s">
         <v>576</v>
@@ -6085,13 +6106,13 @@
         <v>149</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E192" t="s">
         <v>576</v>
@@ -6102,13 +6123,13 @@
         <v>149</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="E193" t="s">
         <v>576</v>
@@ -6119,13 +6140,13 @@
         <v>149</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="E194" t="s">
         <v>576</v>
@@ -6136,13 +6157,13 @@
         <v>149</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="E195" t="s">
         <v>576</v>
@@ -6153,13 +6174,13 @@
         <v>149</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E196" t="s">
         <v>576</v>
@@ -6170,13 +6191,13 @@
         <v>149</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="E197" t="s">
         <v>576</v>
@@ -6187,13 +6208,13 @@
         <v>149</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="E198" t="s">
         <v>576</v>
@@ -6204,13 +6225,13 @@
         <v>149</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="E199" t="s">
         <v>576</v>
@@ -6221,13 +6242,13 @@
         <v>149</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="E200" t="s">
         <v>576</v>
@@ -6238,13 +6259,13 @@
         <v>149</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E201" t="s">
         <v>576</v>
@@ -6255,13 +6276,13 @@
         <v>149</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="E202" t="s">
         <v>576</v>
@@ -6272,13 +6293,13 @@
         <v>149</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>615</v>
+        <v>488</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>616</v>
+        <v>489</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>635</v>
+        <v>490</v>
       </c>
       <c r="E203" t="s">
         <v>576</v>
@@ -6289,13 +6310,13 @@
         <v>149</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>617</v>
+        <v>468</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>618</v>
+        <v>491</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>629</v>
+        <v>494</v>
       </c>
       <c r="E204" t="s">
         <v>576</v>
@@ -6306,13 +6327,13 @@
         <v>149</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="E205" t="s">
         <v>576</v>
@@ -6323,13 +6344,13 @@
         <v>149</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E206" t="s">
         <v>576</v>
@@ -6340,13 +6361,13 @@
         <v>149</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E207" t="s">
         <v>576</v>
@@ -6357,13 +6378,13 @@
         <v>149</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E208" t="s">
         <v>576</v>
@@ -6374,13 +6395,13 @@
         <v>149</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E209" t="s">
         <v>576</v>
@@ -6391,13 +6412,13 @@
         <v>149</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>736</v>
+        <v>633</v>
       </c>
       <c r="E210" t="s">
         <v>576</v>
@@ -6408,13 +6429,13 @@
         <v>149</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>737</v>
+        <v>634</v>
       </c>
       <c r="E211" t="s">
         <v>576</v>
@@ -6425,13 +6446,13 @@
         <v>149</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E212" t="s">
         <v>576</v>
@@ -6442,13 +6463,13 @@
         <v>149</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="E213" t="s">
         <v>576</v>
@@ -6459,13 +6480,13 @@
         <v>149</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="E214" t="s">
         <v>576</v>
@@ -6476,13 +6497,13 @@
         <v>149</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="E215" t="s">
         <v>576</v>
@@ -6493,13 +6514,13 @@
         <v>149</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E216" t="s">
         <v>576</v>
@@ -6510,64 +6531,64 @@
         <v>149</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E217" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="15" customHeight="1">
+    <row r="218" spans="1:5">
       <c r="A218" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>241</v>
+        <v>649</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>263</v>
+        <v>648</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>271</v>
+        <v>742</v>
       </c>
       <c r="E218" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>242</v>
+        <v>651</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>264</v>
+        <v>650</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>272</v>
+        <v>743</v>
       </c>
       <c r="E219" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" ht="15" customHeight="1">
       <c r="A220" s="2" t="s">
         <v>162</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E220" t="s">
         <v>577</v>
@@ -6578,13 +6599,13 @@
         <v>162</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E221" t="s">
         <v>577</v>
@@ -6595,13 +6616,13 @@
         <v>162</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>254</v>
+        <v>243</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E222" t="s">
         <v>577</v>
@@ -6612,13 +6633,13 @@
         <v>162</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="E223" t="s">
         <v>577</v>
@@ -6629,13 +6650,13 @@
         <v>162</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>266</v>
+        <v>253</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="E224" t="s">
         <v>577</v>
@@ -6646,13 +6667,13 @@
         <v>162</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E225" t="s">
         <v>577</v>
@@ -6663,13 +6684,13 @@
         <v>162</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E226" t="s">
         <v>577</v>
@@ -6680,13 +6701,13 @@
         <v>162</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E227" t="s">
         <v>577</v>
@@ -6697,13 +6718,13 @@
         <v>162</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E228" t="s">
         <v>577</v>
@@ -6714,13 +6735,13 @@
         <v>162</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>560</v>
+        <v>248</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>566</v>
+        <v>269</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E229" t="s">
         <v>577</v>
@@ -6731,13 +6752,13 @@
         <v>162</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>561</v>
+        <v>249</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>567</v>
+        <v>270</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E230" t="s">
         <v>577</v>
@@ -6748,13 +6769,13 @@
         <v>162</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E231" t="s">
         <v>577</v>
@@ -6765,13 +6786,13 @@
         <v>162</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E232" t="s">
         <v>577</v>
@@ -6782,13 +6803,13 @@
         <v>162</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E233" t="s">
         <v>577</v>
@@ -6799,13 +6820,13 @@
         <v>162</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E234" t="s">
         <v>577</v>
@@ -6816,13 +6837,13 @@
         <v>162</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>499</v>
+        <v>564</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>502</v>
+        <v>570</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>500</v>
+        <v>301</v>
       </c>
       <c r="E235" t="s">
         <v>577</v>
@@ -6833,13 +6854,13 @@
         <v>162</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>515</v>
+        <v>565</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>501</v>
+        <v>302</v>
       </c>
       <c r="E236" t="s">
         <v>577</v>
@@ -6850,13 +6871,13 @@
         <v>162</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="E237" t="s">
         <v>577</v>
@@ -6867,13 +6888,13 @@
         <v>162</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="E238" t="s">
         <v>577</v>
@@ -6884,13 +6905,13 @@
         <v>162</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E239" t="s">
         <v>577</v>
@@ -6898,36 +6919,36 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2" t="s">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>3</v>
+        <v>508</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>2</v>
+        <v>509</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>118</v>
+        <v>510</v>
       </c>
       <c r="E240" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2" t="s">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>5</v>
+        <v>511</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>4</v>
+        <v>512</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>767</v>
+        <v>514</v>
       </c>
       <c r="E241" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -6935,13 +6956,13 @@
         <v>80</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E242" t="s">
         <v>579</v>
@@ -6952,13 +6973,13 @@
         <v>80</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>119</v>
+        <v>767</v>
       </c>
       <c r="E243" t="s">
         <v>579</v>
@@ -6969,13 +6990,13 @@
         <v>80</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E244" t="s">
         <v>579</v>
@@ -6986,13 +7007,13 @@
         <v>80</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>766</v>
+        <v>119</v>
       </c>
       <c r="E245" t="s">
         <v>579</v>
@@ -7003,13 +7024,13 @@
         <v>80</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>760</v>
+        <v>11</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>765</v>
+        <v>121</v>
       </c>
       <c r="E246" t="s">
         <v>579</v>
@@ -7020,13 +7041,13 @@
         <v>80</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>96</v>
+        <v>766</v>
       </c>
       <c r="E247" t="s">
         <v>579</v>
@@ -7037,13 +7058,13 @@
         <v>80</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>17</v>
+        <v>760</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>95</v>
+        <v>765</v>
       </c>
       <c r="E248" t="s">
         <v>579</v>
@@ -7054,13 +7075,13 @@
         <v>80</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E249" t="s">
         <v>579</v>
@@ -7071,13 +7092,13 @@
         <v>80</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E250" t="s">
         <v>579</v>
@@ -7088,13 +7109,13 @@
         <v>80</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E251" t="s">
         <v>579</v>
@@ -7105,13 +7126,13 @@
         <v>80</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>764</v>
+        <v>99</v>
       </c>
       <c r="E252" t="s">
         <v>579</v>
@@ -7122,13 +7143,13 @@
         <v>80</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E253" t="s">
         <v>579</v>
@@ -7139,13 +7160,13 @@
         <v>80</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>102</v>
+        <v>764</v>
       </c>
       <c r="E254" t="s">
         <v>579</v>
@@ -7156,13 +7177,13 @@
         <v>80</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E255" t="s">
         <v>579</v>
@@ -7173,13 +7194,13 @@
         <v>80</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E256" t="s">
         <v>579</v>
@@ -7190,13 +7211,13 @@
         <v>80</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E257" t="s">
         <v>579</v>
@@ -7206,14 +7227,14 @@
       <c r="A258" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B258" s="5" t="s">
-        <v>34</v>
+      <c r="B258" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="E258" t="s">
         <v>579</v>
@@ -7224,13 +7245,13 @@
         <v>80</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="E259" t="s">
         <v>579</v>
@@ -7240,14 +7261,14 @@
       <c r="A260" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B260" s="2" t="s">
-        <v>36</v>
+      <c r="B260" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E260" t="s">
         <v>579</v>
@@ -7258,13 +7279,13 @@
         <v>80</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E261" t="s">
         <v>579</v>
@@ -7275,13 +7296,13 @@
         <v>80</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>763</v>
+        <v>36</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="E262" t="s">
         <v>579</v>
@@ -7292,13 +7313,13 @@
         <v>80</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="E263" t="s">
         <v>579</v>
@@ -7309,13 +7330,13 @@
         <v>80</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>39</v>
+        <v>763</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E264" t="s">
         <v>579</v>
@@ -7326,13 +7347,13 @@
         <v>80</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E265" t="s">
         <v>579</v>
@@ -7343,13 +7364,13 @@
         <v>80</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E266" t="s">
         <v>579</v>
@@ -7360,13 +7381,13 @@
         <v>80</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E267" t="s">
         <v>579</v>
@@ -7377,13 +7398,13 @@
         <v>80</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E268" t="s">
         <v>579</v>
@@ -7394,13 +7415,13 @@
         <v>80</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E269" t="s">
         <v>579</v>
@@ -7411,13 +7432,13 @@
         <v>80</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E270" t="s">
         <v>579</v>
@@ -7428,13 +7449,13 @@
         <v>80</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E271" t="s">
         <v>579</v>
@@ -7445,13 +7466,13 @@
         <v>80</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E272" t="s">
         <v>579</v>
@@ -7462,13 +7483,13 @@
         <v>80</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>744</v>
+        <v>46</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>745</v>
+        <v>32</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>750</v>
+        <v>116</v>
       </c>
       <c r="E273" t="s">
         <v>579</v>
@@ -7479,13 +7500,13 @@
         <v>80</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>748</v>
+        <v>47</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>745</v>
+        <v>105</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>751</v>
+        <v>117</v>
       </c>
       <c r="E274" t="s">
         <v>579</v>
@@ -7496,13 +7517,13 @@
         <v>80</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="E275" t="s">
         <v>579</v>
@@ -7513,13 +7534,13 @@
         <v>80</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E276" t="s">
         <v>579</v>
@@ -7527,36 +7548,36 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2" t="s">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>49</v>
+        <v>746</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>48</v>
+        <v>747</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>140</v>
+        <v>753</v>
       </c>
       <c r="E277" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2" t="s">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>51</v>
+        <v>749</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>50</v>
+        <v>747</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>234</v>
+        <v>752</v>
       </c>
       <c r="E278" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -7564,13 +7585,13 @@
         <v>162</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>236</v>
+        <v>140</v>
       </c>
       <c r="E279" t="s">
         <v>577</v>
@@ -7581,13 +7602,13 @@
         <v>162</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E280" t="s">
         <v>577</v>
@@ -7598,13 +7619,13 @@
         <v>162</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E281" t="s">
         <v>577</v>
@@ -7615,13 +7636,13 @@
         <v>162</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E282" t="s">
         <v>577</v>
@@ -7632,13 +7653,13 @@
         <v>162</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>278</v>
+        <v>238</v>
       </c>
       <c r="E283" t="s">
         <v>577</v>
@@ -7649,13 +7670,13 @@
         <v>162</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>141</v>
+        <v>237</v>
       </c>
       <c r="E284" t="s">
         <v>577</v>
@@ -7666,13 +7687,13 @@
         <v>162</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>142</v>
+        <v>278</v>
       </c>
       <c r="E285" t="s">
         <v>577</v>
@@ -7683,13 +7704,13 @@
         <v>162</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E286" t="s">
         <v>577</v>
@@ -7700,13 +7721,13 @@
         <v>162</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E287" t="s">
         <v>577</v>
@@ -7717,13 +7738,13 @@
         <v>162</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E288" t="s">
         <v>577</v>
@@ -7734,13 +7755,13 @@
         <v>162</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E289" t="s">
         <v>577</v>
@@ -7751,13 +7772,13 @@
         <v>162</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E290" t="s">
         <v>577</v>
@@ -7768,13 +7789,13 @@
         <v>162</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E291" t="s">
         <v>577</v>
@@ -7785,15 +7806,49 @@
         <v>162</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E292" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E293" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B294" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="C294" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D292" s="2" t="s">
+      <c r="D294" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E292" t="s">
+      <c r="E294" t="s">
         <v>577</v>
       </c>
     </row>
